--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SANDÁ C.B. L´HOSPITALET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SANDÁ C.B. L´HOSPITALET.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>82.2355</v>
+        <v>82.9096</v>
       </c>
       <c r="E2" t="n">
-        <v>59.0052</v>
+        <v>62.2133</v>
       </c>
       <c r="F2" t="n">
-        <v>23.2307</v>
+        <v>20.6963</v>
       </c>
       <c r="G2" t="n">
         <v>50.4681</v>
@@ -610,13 +610,13 @@
         <v>46.4218</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4339</v>
+        <v>6.1078</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.6898</v>
+        <v>0.5183000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>8.123699999999999</v>
+        <v>5.5893</v>
       </c>
       <c r="V2" t="n">
         <v>53.1158</v>
@@ -643,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>59.1757</v>
+        <v>60.4057</v>
       </c>
       <c r="E3" t="n">
-        <v>42.5296</v>
+        <v>43.5725</v>
       </c>
       <c r="F3" t="n">
-        <v>16.6459</v>
+        <v>16.8328</v>
       </c>
       <c r="G3" t="n">
         <v>28.4984</v>
@@ -688,13 +688,13 @@
         <v>42.4541</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7281</v>
+        <v>2.9581</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2163</v>
+        <v>-0.1729999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9442</v>
+        <v>3.1315</v>
       </c>
       <c r="V3" t="n">
         <v>34.5038</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>50.283</v>
+        <v>50.5261</v>
       </c>
       <c r="E4" t="n">
-        <v>36.2599</v>
+        <v>40.9525</v>
       </c>
       <c r="F4" t="n">
-        <v>14.023</v>
+        <v>9.573600000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>24.8604</v>
+        <v>32.8721</v>
       </c>
       <c r="H4" t="n">
-        <v>18.2753</v>
+        <v>-5.289499999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>6.585</v>
+        <v>38.1616</v>
       </c>
       <c r="J4" t="n">
-        <v>38.1667</v>
+        <v>48.6375</v>
       </c>
       <c r="K4" t="n">
-        <v>26.8812</v>
+        <v>11.4633</v>
       </c>
       <c r="L4" t="n">
-        <v>11.2851</v>
+        <v>37.1746</v>
       </c>
       <c r="M4" t="n">
-        <v>-13.3063</v>
+        <v>-15.7657</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.6059</v>
+        <v>-16.7529</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.7004</v>
+        <v>0.9874000000000002</v>
       </c>
       <c r="P4" t="n">
-        <v>1.587</v>
+        <v>22.0208</v>
       </c>
       <c r="Q4" t="n">
-        <v>-35.907</v>
+        <v>-19.0446</v>
       </c>
       <c r="R4" t="n">
-        <v>37.4948</v>
+        <v>41.0655</v>
       </c>
       <c r="S4" t="n">
-        <v>24.0193</v>
+        <v>-7.7771</v>
       </c>
       <c r="T4" t="n">
-        <v>16.9728</v>
+        <v>-3.3648</v>
       </c>
       <c r="U4" t="n">
-        <v>7.0467</v>
+        <v>-4.4124</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1843000000000003</v>
+        <v>3.4104</v>
       </c>
       <c r="W4" t="n">
-        <v>17.0278</v>
+        <v>14.7246</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.2123</v>
+        <v>-11.3141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>31.793</v>
+        <v>35.2591</v>
       </c>
       <c r="E5" t="n">
-        <v>31.2654</v>
+        <v>24.4642</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5276000000000001</v>
+        <v>10.7953</v>
       </c>
       <c r="G5" t="n">
-        <v>32.8721</v>
+        <v>24.8604</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.289499999999999</v>
+        <v>18.2753</v>
       </c>
       <c r="I5" t="n">
-        <v>38.1616</v>
+        <v>6.585</v>
       </c>
       <c r="J5" t="n">
-        <v>48.6375</v>
+        <v>38.1667</v>
       </c>
       <c r="K5" t="n">
-        <v>11.4633</v>
+        <v>26.8812</v>
       </c>
       <c r="L5" t="n">
-        <v>37.1746</v>
+        <v>11.2851</v>
       </c>
       <c r="M5" t="n">
-        <v>-15.7657</v>
+        <v>-13.3063</v>
       </c>
       <c r="N5" t="n">
-        <v>-16.7529</v>
+        <v>-8.6059</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9874000000000002</v>
+        <v>-4.7004</v>
       </c>
       <c r="P5" t="n">
-        <v>22.0208</v>
+        <v>1.587</v>
       </c>
       <c r="Q5" t="n">
-        <v>-19.0446</v>
+        <v>-35.907</v>
       </c>
       <c r="R5" t="n">
-        <v>41.0655</v>
+        <v>37.4948</v>
       </c>
       <c r="S5" t="n">
-        <v>-26.5103</v>
+        <v>8.996</v>
       </c>
       <c r="T5" t="n">
-        <v>-13.0517</v>
+        <v>5.1772</v>
       </c>
       <c r="U5" t="n">
-        <v>-13.4584</v>
+        <v>3.8184</v>
       </c>
       <c r="V5" t="n">
-        <v>3.4104</v>
+        <v>-0.1843000000000003</v>
       </c>
       <c r="W5" t="n">
-        <v>14.7246</v>
+        <v>17.0278</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.3141</v>
+        <v>-17.2123</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>17.2112</v>
+        <v>27.0313</v>
       </c>
       <c r="E6" t="n">
-        <v>28.1324</v>
+        <v>31.2894</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.9207</v>
+        <v>-4.257999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>43.2768</v>
@@ -922,13 +922,13 @@
         <v>34.9157</v>
       </c>
       <c r="S6" t="n">
-        <v>-14.1322</v>
+        <v>-4.3126</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.076</v>
+        <v>0.08120000000000019</v>
       </c>
       <c r="U6" t="n">
-        <v>-11.0562</v>
+        <v>-4.393899999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.5652000000000001</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>14.7544</v>
+        <v>23.3121</v>
       </c>
       <c r="E7" t="n">
-        <v>9.3872</v>
+        <v>23.2083</v>
       </c>
       <c r="F7" t="n">
-        <v>5.3667</v>
+        <v>0.1040000000000005</v>
       </c>
       <c r="G7" t="n">
-        <v>18.7218</v>
+        <v>9.596500000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>13.395</v>
+        <v>-17.0979</v>
       </c>
       <c r="I7" t="n">
-        <v>5.326499999999999</v>
+        <v>26.6941</v>
       </c>
       <c r="J7" t="n">
-        <v>26.1707</v>
+        <v>26.0763</v>
       </c>
       <c r="K7" t="n">
-        <v>19.3421</v>
+        <v>1.606000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8282</v>
+        <v>24.4702</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.448700000000001</v>
+        <v>-16.4801</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.947299999999999</v>
+        <v>-18.704</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5015</v>
+        <v>2.2241</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.1741</v>
+        <v>-10.9112</v>
       </c>
       <c r="Q7" t="n">
-        <v>-27.1783</v>
+        <v>-43.8423</v>
       </c>
       <c r="R7" t="n">
-        <v>24.0047</v>
+        <v>32.9318</v>
       </c>
       <c r="S7" t="n">
-        <v>-6.3858</v>
+        <v>2.0558</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.189</v>
+        <v>-3.2177</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.1968</v>
+        <v>5.2731</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5926</v>
+        <v>22.5713</v>
       </c>
       <c r="W7" t="n">
-        <v>11.5849</v>
+        <v>44.1925</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.9922</v>
+        <v>-21.6213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>13.5361</v>
+        <v>19.3175</v>
       </c>
       <c r="E8" t="n">
-        <v>15.1083</v>
+        <v>10.1299</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5717</v>
+        <v>9.1875</v>
       </c>
       <c r="G8" t="n">
-        <v>9.596500000000001</v>
+        <v>18.7218</v>
       </c>
       <c r="H8" t="n">
-        <v>-17.0979</v>
+        <v>13.395</v>
       </c>
       <c r="I8" t="n">
-        <v>26.6941</v>
+        <v>5.326499999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>26.0763</v>
+        <v>26.1707</v>
       </c>
       <c r="K8" t="n">
-        <v>1.606000000000001</v>
+        <v>19.3421</v>
       </c>
       <c r="L8" t="n">
-        <v>24.4702</v>
+        <v>6.8282</v>
       </c>
       <c r="M8" t="n">
-        <v>-16.4801</v>
+        <v>-7.448700000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-18.704</v>
+        <v>-5.947299999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2241</v>
+        <v>-1.5015</v>
       </c>
       <c r="P8" t="n">
-        <v>-10.9112</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q8" t="n">
-        <v>-43.8423</v>
+        <v>-27.1783</v>
       </c>
       <c r="R8" t="n">
-        <v>32.9318</v>
+        <v>24.0047</v>
       </c>
       <c r="S8" t="n">
-        <v>-7.7202</v>
+        <v>-1.8226</v>
       </c>
       <c r="T8" t="n">
-        <v>-11.3173</v>
+        <v>-0.4467999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5975</v>
+        <v>-1.3756</v>
       </c>
       <c r="V8" t="n">
-        <v>22.5713</v>
+        <v>5.5926</v>
       </c>
       <c r="W8" t="n">
-        <v>44.1925</v>
+        <v>11.5849</v>
       </c>
       <c r="X8" t="n">
-        <v>-21.6213</v>
+        <v>-5.9922</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>11.8279</v>
+        <v>13.7884</v>
       </c>
       <c r="E9" t="n">
-        <v>17.3202</v>
+        <v>16.5603</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.4919</v>
+        <v>-2.772199999999999</v>
       </c>
       <c r="G9" t="n">
         <v>8.770200000000001</v>
@@ -1156,13 +1156,13 @@
         <v>19.4415</v>
       </c>
       <c r="S9" t="n">
-        <v>1.082</v>
+        <v>3.0423</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1409</v>
+        <v>0.3811999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0585</v>
+        <v>2.6612</v>
       </c>
       <c r="V9" t="n">
         <v>-2.5868</v>
@@ -1189,13 +1189,13 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>11.2867</v>
+        <v>5.4453</v>
       </c>
       <c r="E10" t="n">
-        <v>4.9894</v>
+        <v>-0.6733000000000002</v>
       </c>
       <c r="F10" t="n">
-        <v>6.2973</v>
+        <v>6.1187</v>
       </c>
       <c r="G10" t="n">
         <v>11.233</v>
@@ -1234,13 +1234,13 @@
         <v>17.6562</v>
       </c>
       <c r="S10" t="n">
-        <v>9.2727</v>
+        <v>3.4317</v>
       </c>
       <c r="T10" t="n">
-        <v>6.536600000000001</v>
+        <v>0.8738000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7365</v>
+        <v>2.5578</v>
       </c>
       <c r="V10" t="n">
         <v>-3.069500000000001</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PEREZ</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1547</v>
+        <v>1.7423</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.152000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1547</v>
+        <v>2.894200000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.136</v>
+        <v>19.5417</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>9.5801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.136</v>
+        <v>9.9621</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>27.7931</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>17.3857</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>10.4077</v>
       </c>
       <c r="M11" t="n">
-        <v>0.136</v>
+        <v>-8.251300000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-7.805800000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.136</v>
+        <v>-0.4460000000000002</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-13.2916</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-29.3608</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>16.069</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0187</v>
+        <v>1.5243</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1.2517</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0187</v>
+        <v>2.776</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-6.0323</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.6672</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-7.6995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. CANOVAS PEREZ</t>
+          <t>P. RODRIGUEZ PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,61 +1342,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0532</v>
+        <v>0.1828</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8403</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.787</v>
+        <v>0.1828</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1666</v>
+        <v>0.136</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2014</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3679</v>
+        <v>0.136</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5795</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0605</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.413</v>
+        <v>0.136</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1409</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2721</v>
+        <v>0.136</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3117</v>
+        <v>0.0468</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0623</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.374</v>
+        <v>0.0468</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>B. CANOVAS PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,61 +1420,61 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9919</v>
+        <v>-0.05319999999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9919</v>
+        <v>-0.8403</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.7871</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.1666</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.2014</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.3679</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.5795</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.1409</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.2721</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.3118</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.0623</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.3741</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VICENS MOREY</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.7177</v>
+        <v>-0.9919</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8936</v>
+        <v>-0.9919</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.6113</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1064</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9809</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8745000000000001</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>6.3636</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9905</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3731</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.2572</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.0096</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2477</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.3725</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.9596</v>
+        <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7176</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7347</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2659</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. VICENS MOREY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.681399999999999</v>
+        <v>-2.3487</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1727999999999996</v>
+        <v>3.1826</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5084</v>
+        <v>-5.5314</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.413</v>
+        <v>1.1064</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.6135</v>
+        <v>1.9809</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2006</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6646</v>
+        <v>6.3636</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2672</v>
+        <v>4.9905</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9319</v>
+        <v>1.3731</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.0777</v>
+        <v>-5.2572</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.3463</v>
+        <v>-3.0096</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7313000000000002</v>
+        <v>-2.2477</v>
       </c>
       <c r="P15" t="n">
+        <v>-3.3725</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-4.9596</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-16.8626</v>
-      </c>
       <c r="R15" t="n">
-        <v>11.9032</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>8.8355</v>
+        <v>-0.3486</v>
       </c>
       <c r="T15" t="n">
-        <v>6.8651</v>
+        <v>0.3062</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9703</v>
+        <v>-0.6548</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1443</v>
+        <v>0.2659</v>
       </c>
       <c r="W15" t="n">
-        <v>8.1602</v>
+        <v>1.4724</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.3045</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.748699999999999</v>
+        <v>-3.6789</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3695999999999999</v>
+        <v>-0.001199999999999868</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.3791</v>
+        <v>-3.6777</v>
       </c>
       <c r="G16" t="n">
         <v>3.3065</v>
@@ -1702,13 +1702,13 @@
         <v>2.3807</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8360000000000001</v>
+        <v>0.2337</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6176</v>
+        <v>-0.2492</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2184</v>
+        <v>0.4832000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-6.4256</v>
@@ -1735,13 +1735,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.6704</v>
+        <v>-4.89</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.1487</v>
+        <v>-4.5366</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5216000000000001</v>
+        <v>-0.3533000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1486</v>
@@ -1780,13 +1780,13 @@
         <v>0.992</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2027</v>
+        <v>-0.4223</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1107</v>
+        <v>-0.4986</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0919</v>
+        <v>0.07650000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3271</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.879300000000001</v>
+        <v>-9.637599999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.9168</v>
+        <v>-5.5746</v>
       </c>
       <c r="F18" t="n">
-        <v>1.037500000000001</v>
+        <v>-4.062799999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>19.5417</v>
+        <v>-5.413</v>
       </c>
       <c r="H18" t="n">
-        <v>9.5801</v>
+        <v>-7.6135</v>
       </c>
       <c r="I18" t="n">
-        <v>9.9621</v>
+        <v>2.2006</v>
       </c>
       <c r="J18" t="n">
-        <v>27.7931</v>
+        <v>1.6646</v>
       </c>
       <c r="K18" t="n">
-        <v>17.3857</v>
+        <v>-1.2672</v>
       </c>
       <c r="L18" t="n">
-        <v>10.4077</v>
+        <v>2.9319</v>
       </c>
       <c r="M18" t="n">
-        <v>-8.251300000000001</v>
+        <v>-7.0777</v>
       </c>
       <c r="N18" t="n">
-        <v>-7.805800000000001</v>
+        <v>-6.3463</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4460000000000002</v>
+        <v>-0.7313000000000002</v>
       </c>
       <c r="P18" t="n">
-        <v>-13.2916</v>
+        <v>-4.9596</v>
       </c>
       <c r="Q18" t="n">
-        <v>-29.3608</v>
+        <v>-16.8626</v>
       </c>
       <c r="R18" t="n">
-        <v>16.069</v>
+        <v>11.9032</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.0972</v>
+        <v>2.8792</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.016500000000001</v>
+        <v>1.4632</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9193</v>
+        <v>1.4161</v>
       </c>
       <c r="V18" t="n">
-        <v>-6.0323</v>
+        <v>-2.1443</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6672</v>
+        <v>8.1602</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.6995</v>
+        <v>-10.3045</v>
       </c>
     </row>
     <row r="19">
@@ -1891,19 +1891,19 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>268.5156</v>
+        <v>298.3199</v>
       </c>
       <c r="E19" t="n">
-        <v>232.4511</v>
+        <v>241.8031</v>
       </c>
       <c r="F19" t="n">
-        <v>36.0657</v>
+        <v>56.51689999999999</v>
       </c>
       <c r="G19" t="n">
         <v>244.6597</v>
       </c>
       <c r="H19" t="n">
-        <v>68.49350000000001</v>
+        <v>68.4935</v>
       </c>
       <c r="I19" t="n">
         <v>176.1653</v>
@@ -1924,10 +1924,10 @@
         <v>-132.8115</v>
       </c>
       <c r="O19" t="n">
-        <v>-18.95920000000001</v>
+        <v>-18.9592</v>
       </c>
       <c r="P19" t="n">
-        <v>-61.4983</v>
+        <v>-61.49829999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>-390.8138</v>
@@ -1936,13 +1936,13 @@
         <v>329.3181</v>
       </c>
       <c r="S19" t="n">
-        <v>-12.90010000000001</v>
+        <v>16.9043</v>
       </c>
       <c r="T19" t="n">
-        <v>-9.814699999999998</v>
+        <v>-0.4629999999999983</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.084000000000001</v>
+        <v>17.3673</v>
       </c>
       <c r="V19" t="n">
         <v>98.2551</v>
